--- a/param/vaccine_sensitivity analysis_2.xlsx
+++ b/param/vaccine_sensitivity analysis_2.xlsx
@@ -1,20 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23080" windowHeight="10640"/>
+    <workbookView windowWidth="26320" windowHeight="13980"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="38">
   <si>
     <t>name</t>
   </si>
@@ -104,6 +117,12 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>limit</t>
+  </si>
+  <si>
+    <t>Inf</t>
   </si>
   <si>
     <t>HPV</t>
@@ -1059,8 +1078,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
+  <dimension ref="A1:AA9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="16384" width="10.1607142857143" style="1" customWidth="1"/>
   </cols>
@@ -1183,10 +1202,10 @@
         <v>29</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>29</v>
@@ -1222,10 +1241,10 @@
         <v>29</v>
       </c>
       <c r="Y2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="AA2" s="1" t="s">
         <v>29</v>
@@ -1236,13 +1255,13 @@
         <v>30</v>
       </c>
       <c r="B3" s="1">
-        <v>4.09e-5</v>
+        <v>0</v>
       </c>
       <c r="C3" s="1">
-        <v>2.14e-5</v>
+        <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>0.0006275</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>29</v>
@@ -1251,7 +1270,7 @@
         <v>29</v>
       </c>
       <c r="G3" s="1">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>29</v>
@@ -1265,23 +1284,23 @@
       <c r="K3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>29</v>
+      <c r="L3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="1">
+        <v>-1</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="1">
-        <v>9.95e-5</v>
-      </c>
-      <c r="P3" s="1">
-        <v>4.84e-5</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>0.00147</v>
+      <c r="O3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>29</v>
@@ -1290,7 +1309,7 @@
         <v>29</v>
       </c>
       <c r="T3" s="1">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="U3" s="1" t="s">
         <v>29</v>
@@ -1304,11 +1323,11 @@
       <c r="X3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Y3" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>29</v>
+      <c r="Y3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>1</v>
       </c>
       <c r="AA3" s="1" t="s">
         <v>29</v>
@@ -1316,16 +1335,16 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:27">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="1">
-        <v>0.0001049</v>
+        <v>4.09e-5</v>
       </c>
       <c r="C4" s="1">
-        <v>4e-7</v>
+        <v>2.14e-5</v>
       </c>
       <c r="D4" s="1">
-        <v>4.22e-5</v>
+        <v>0.0006275</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>29</v>
@@ -1334,7 +1353,7 @@
         <v>29</v>
       </c>
       <c r="G4" s="1">
-        <v>0.77</v>
+        <v>0.33</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>29</v>
@@ -1348,23 +1367,23 @@
       <c r="K4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>29</v>
+      <c r="L4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0.23</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>29</v>
       </c>
       <c r="O4" s="1">
-        <v>0.0001049</v>
+        <v>9.95e-5</v>
       </c>
       <c r="P4" s="1">
-        <v>4e-7</v>
+        <v>4.84e-5</v>
       </c>
       <c r="Q4" s="1">
-        <v>7.2e-5</v>
+        <v>0.00147</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>29</v>
@@ -1373,7 +1392,7 @@
         <v>29</v>
       </c>
       <c r="T4" s="1">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="U4" s="1" t="s">
         <v>29</v>
@@ -1387,11 +1406,11 @@
       <c r="X4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Y4" s="1">
-        <v>0.83</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>29</v>
+      <c r="Y4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0.45</v>
       </c>
       <c r="AA4" s="1" t="s">
         <v>29</v>
@@ -1399,16 +1418,16 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:27">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="1">
-        <v>0.0080363</v>
+        <v>0.0001049</v>
       </c>
       <c r="C5" s="1">
-        <v>3.3e-6</v>
+        <v>4e-7</v>
       </c>
       <c r="D5" s="1">
-        <v>3.39e-5</v>
+        <v>4.22e-5</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>29</v>
@@ -1417,7 +1436,7 @@
         <v>29</v>
       </c>
       <c r="G5" s="1">
-        <v>0.968</v>
+        <v>0.77</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>29</v>
@@ -1431,23 +1450,23 @@
       <c r="K5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="1">
-        <v>0.12</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>29</v>
+      <c r="L5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0.71</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>29</v>
       </c>
       <c r="O5" s="1">
-        <v>0.0100049</v>
+        <v>0.0001049</v>
       </c>
       <c r="P5" s="1">
-        <v>4.4e-6</v>
+        <v>4e-7</v>
       </c>
       <c r="Q5" s="1">
-        <v>7.08e-5</v>
+        <v>7.2e-5</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>29</v>
@@ -1456,7 +1475,7 @@
         <v>29</v>
       </c>
       <c r="T5" s="1">
-        <v>0.988</v>
+        <v>0.86</v>
       </c>
       <c r="U5" s="1" t="s">
         <v>29</v>
@@ -1470,11 +1489,11 @@
       <c r="X5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Y5" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>29</v>
+      <c r="Y5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>0.83</v>
       </c>
       <c r="AA5" s="1" t="s">
         <v>29</v>
@@ -1482,16 +1501,16 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:27">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="1">
-        <v>0.0001677</v>
+        <v>0.0080363</v>
       </c>
       <c r="C6" s="1">
-        <v>8e-7</v>
+        <v>3.3e-6</v>
       </c>
       <c r="D6" s="1">
-        <v>7.04e-5</v>
+        <v>3.39e-5</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>29</v>
@@ -1500,7 +1519,7 @@
         <v>29</v>
       </c>
       <c r="G6" s="1">
-        <v>0.755</v>
+        <v>0.968</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>29</v>
@@ -1514,23 +1533,23 @@
       <c r="K6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>29</v>
+      <c r="L6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0.12</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="O6" s="1">
-        <v>0.0002801</v>
+        <v>0.0100049</v>
       </c>
       <c r="P6" s="1">
-        <v>1.2e-6</v>
+        <v>4.4e-6</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.0001021</v>
+        <v>7.08e-5</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>29</v>
@@ -1539,7 +1558,7 @@
         <v>29</v>
       </c>
       <c r="T6" s="1">
-        <v>0.923</v>
+        <v>0.988</v>
       </c>
       <c r="U6" s="1" t="s">
         <v>29</v>
@@ -1553,11 +1572,11 @@
       <c r="X6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Y6" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>29</v>
+      <c r="Y6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0.15</v>
       </c>
       <c r="AA6" s="1" t="s">
         <v>29</v>
@@ -1565,16 +1584,16 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:27">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1">
-        <v>0.0002905</v>
+        <v>0.0001677</v>
       </c>
       <c r="C7" s="1">
-        <v>1.4e-6</v>
+        <v>8e-7</v>
       </c>
       <c r="D7" s="1">
-        <v>0.0001213</v>
+        <v>7.04e-5</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>29</v>
@@ -1583,7 +1602,7 @@
         <v>29</v>
       </c>
       <c r="G7" s="1">
-        <v>0.9598</v>
+        <v>0.755</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>29</v>
@@ -1597,23 +1616,23 @@
       <c r="K7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="1">
-        <v>0.41</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>29</v>
+      <c r="L7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0.6</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>29</v>
       </c>
       <c r="O7" s="1">
-        <v>0.0004854</v>
+        <v>0.0002801</v>
       </c>
       <c r="P7" s="1">
-        <v>2e-6</v>
+        <v>1.2e-6</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.0001759</v>
+        <v>0.0001021</v>
       </c>
       <c r="R7" s="1" t="s">
         <v>29</v>
@@ -1622,7 +1641,7 @@
         <v>29</v>
       </c>
       <c r="T7" s="1">
-        <v>0.9971</v>
+        <v>0.923</v>
       </c>
       <c r="U7" s="1" t="s">
         <v>29</v>
@@ -1636,11 +1655,11 @@
       <c r="X7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Y7" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>29</v>
+      <c r="Y7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>0.68</v>
       </c>
       <c r="AA7" s="1" t="s">
         <v>29</v>
@@ -1648,84 +1667,167 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="1:27">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" s="1">
+        <v>0.0002905</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1.4e-6</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.0001213</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.9598</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0.0004854</v>
+      </c>
+      <c r="P8" s="1">
+        <v>2e-6</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0.0001759</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0.9971</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:27">
+      <c r="A9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="1">
         <v>0.05</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C9" s="1">
         <v>6.9e-5</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D9" s="1">
         <v>0.0024999</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="1">
+      <c r="E9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="1">
         <v>0.37</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" s="1">
+      <c r="H9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="1">
         <v>-0.2</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O8" s="1">
+      <c r="N9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9" s="1">
         <v>0.1</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P9" s="1">
         <v>0.000172</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q9" s="1">
         <v>0.0032269</v>
       </c>
-      <c r="R8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T8" s="1">
+      <c r="R9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T9" s="1">
         <v>0.94</v>
       </c>
-      <c r="U8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y8" s="1">
+      <c r="U9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z9" s="1">
         <v>-0.14</v>
       </c>
-      <c r="Z8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA8" s="1" t="s">
+      <c r="AA9" s="1" t="s">
         <v>29</v>
       </c>
     </row>
